--- a/Lab_4/data/partB/param_optimization_process/v150_k10_s100_results.xlsx
+++ b/Lab_4/data/partB/param_optimization_process/v150_k10_s100_results.xlsx
@@ -518,25 +518,25 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="C2" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="D2" t="n">
+        <v>2</v>
+      </c>
+      <c r="E2" t="n">
         <v>1</v>
       </c>
-      <c r="E2" t="n">
-        <v>2</v>
-      </c>
       <c r="F2" t="n">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="G2" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="H2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I2" t="n">
         <v>28</v>
@@ -545,22 +545,22 @@
         <v>1</v>
       </c>
       <c r="K2" t="n">
+        <v>10</v>
+      </c>
+      <c r="L2" t="n">
+        <v>2</v>
+      </c>
+      <c r="M2" t="n">
+        <v>7</v>
+      </c>
+      <c r="N2" t="n">
+        <v>1</v>
+      </c>
+      <c r="O2" t="n">
+        <v>0</v>
+      </c>
+      <c r="P2" t="n">
         <v>5</v>
-      </c>
-      <c r="L2" t="n">
-        <v>1</v>
-      </c>
-      <c r="M2" t="n">
-        <v>6</v>
-      </c>
-      <c r="N2" t="n">
-        <v>3</v>
-      </c>
-      <c r="O2" t="n">
-        <v>2</v>
-      </c>
-      <c r="P2" t="n">
-        <v>3</v>
       </c>
     </row>
     <row r="3">
@@ -570,37 +570,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C3" t="n">
-        <v>71</v>
+        <v>67</v>
       </c>
       <c r="D3" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E3" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F3" t="n">
         <v>1</v>
       </c>
       <c r="G3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H3" t="n">
         <v>0</v>
       </c>
       <c r="I3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J3" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="K3" t="n">
         <v>0</v>
       </c>
       <c r="L3" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="M3" t="n">
         <v>0</v>
@@ -609,10 +609,10 @@
         <v>0</v>
       </c>
       <c r="O3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="P3" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="4">
@@ -628,7 +628,7 @@
         <v>0</v>
       </c>
       <c r="D4" t="n">
-        <v>98</v>
+        <v>85</v>
       </c>
       <c r="E4" t="n">
         <v>0</v>
@@ -646,13 +646,13 @@
         <v>0</v>
       </c>
       <c r="J4" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="K4" t="n">
         <v>0</v>
       </c>
       <c r="L4" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="M4" t="n">
         <v>0</v>
@@ -661,7 +661,7 @@
         <v>0</v>
       </c>
       <c r="O4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P4" t="n">
         <v>0</v>
@@ -674,49 +674,49 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C5" t="n">
-        <v>28</v>
+        <v>36</v>
       </c>
       <c r="D5" t="n">
         <v>0</v>
       </c>
       <c r="E5" t="n">
-        <v>42</v>
+        <v>27</v>
       </c>
       <c r="F5" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="G5" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="H5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I5" t="n">
         <v>1</v>
       </c>
-      <c r="I5" t="n">
+      <c r="J5" t="n">
+        <v>6</v>
+      </c>
+      <c r="K5" t="n">
         <v>0</v>
       </c>
-      <c r="J5" t="n">
-        <v>4</v>
-      </c>
-      <c r="K5" t="n">
-        <v>1</v>
-      </c>
       <c r="L5" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="M5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="N5" t="n">
         <v>3</v>
       </c>
       <c r="O5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="P5" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
     </row>
     <row r="6">
@@ -726,31 +726,31 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="C6" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="D6" t="n">
         <v>0</v>
       </c>
       <c r="E6" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F6" t="n">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="G6" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="H6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I6" t="n">
         <v>3</v>
       </c>
       <c r="J6" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="K6" t="n">
         <v>2</v>
@@ -759,16 +759,16 @@
         <v>4</v>
       </c>
       <c r="M6" t="n">
+        <v>7</v>
+      </c>
+      <c r="N6" t="n">
+        <v>9</v>
+      </c>
+      <c r="O6" t="n">
+        <v>3</v>
+      </c>
+      <c r="P6" t="n">
         <v>10</v>
-      </c>
-      <c r="N6" t="n">
-        <v>18</v>
-      </c>
-      <c r="O6" t="n">
-        <v>4</v>
-      </c>
-      <c r="P6" t="n">
-        <v>3</v>
       </c>
     </row>
     <row r="7">
@@ -787,40 +787,40 @@
         <v>0</v>
       </c>
       <c r="E7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F7" t="n">
-        <v>22</v>
+        <v>9</v>
       </c>
       <c r="G7" t="n">
-        <v>53</v>
+        <v>60</v>
       </c>
       <c r="H7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I7" t="n">
         <v>4</v>
       </c>
       <c r="J7" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K7" t="n">
         <v>3</v>
       </c>
       <c r="L7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M7" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="N7" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="O7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P7" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
     </row>
     <row r="8">
@@ -830,46 +830,46 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="C8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D8" t="n">
         <v>0</v>
       </c>
       <c r="E8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F8" t="n">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="G8" t="n">
+        <v>16</v>
+      </c>
+      <c r="H8" t="n">
         <v>14</v>
       </c>
-      <c r="H8" t="n">
-        <v>8</v>
-      </c>
       <c r="I8" t="n">
-        <v>26</v>
+        <v>36</v>
       </c>
       <c r="J8" t="n">
         <v>0</v>
       </c>
       <c r="K8" t="n">
-        <v>17</v>
+        <v>8</v>
       </c>
       <c r="L8" t="n">
         <v>0</v>
       </c>
       <c r="M8" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="N8" t="n">
         <v>1</v>
       </c>
       <c r="O8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="P8" t="n">
         <v>1</v>
@@ -882,49 +882,49 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C9" t="n">
         <v>1</v>
       </c>
       <c r="D9" t="n">
+        <v>1</v>
+      </c>
+      <c r="E9" t="n">
         <v>0</v>
       </c>
-      <c r="E9" t="n">
-        <v>1</v>
-      </c>
       <c r="F9" t="n">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="G9" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H9" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="I9" t="n">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="J9" t="n">
         <v>0</v>
       </c>
       <c r="K9" t="n">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="L9" t="n">
         <v>1</v>
       </c>
       <c r="M9" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="N9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O9" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="P9" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="10">
@@ -937,13 +937,13 @@
         <v>0</v>
       </c>
       <c r="C10" t="n">
-        <v>20</v>
+        <v>8</v>
       </c>
       <c r="D10" t="n">
-        <v>19</v>
+        <v>4</v>
       </c>
       <c r="E10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F10" t="n">
         <v>0</v>
@@ -958,22 +958,22 @@
         <v>0</v>
       </c>
       <c r="J10" t="n">
-        <v>46</v>
+        <v>72</v>
       </c>
       <c r="K10" t="n">
         <v>0</v>
       </c>
       <c r="L10" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="M10" t="n">
         <v>0</v>
       </c>
       <c r="N10" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="O10" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="P10" t="n">
         <v>0</v>
@@ -986,7 +986,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="C11" t="n">
         <v>0</v>
@@ -1001,19 +1001,19 @@
         <v>7</v>
       </c>
       <c r="G11" t="n">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="H11" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I11" t="n">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="J11" t="n">
         <v>1</v>
       </c>
       <c r="K11" t="n">
-        <v>40</v>
+        <v>33</v>
       </c>
       <c r="L11" t="n">
         <v>0</v>
@@ -1025,10 +1025,10 @@
         <v>2</v>
       </c>
       <c r="O11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="12">
@@ -1041,16 +1041,16 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>34</v>
+        <v>17</v>
       </c>
       <c r="D12" t="n">
-        <v>26</v>
+        <v>5</v>
       </c>
       <c r="E12" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F12" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G12" t="n">
         <v>0</v>
@@ -1059,16 +1059,16 @@
         <v>0</v>
       </c>
       <c r="I12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J12" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="K12" t="n">
         <v>0</v>
       </c>
       <c r="L12" t="n">
-        <v>15</v>
+        <v>50</v>
       </c>
       <c r="M12" t="n">
         <v>0</v>
@@ -1096,37 +1096,37 @@
         <v>0</v>
       </c>
       <c r="D13" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E13" t="n">
         <v>0</v>
       </c>
       <c r="F13" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="G13" t="n">
         <v>6</v>
       </c>
       <c r="H13" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I13" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J13" t="n">
         <v>2</v>
       </c>
       <c r="K13" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="L13" t="n">
         <v>0</v>
       </c>
       <c r="M13" t="n">
-        <v>54</v>
+        <v>62</v>
       </c>
       <c r="N13" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="O13" t="n">
         <v>4</v>
@@ -1142,10 +1142,10 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C14" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D14" t="n">
         <v>2</v>
@@ -1163,28 +1163,28 @@
         <v>0</v>
       </c>
       <c r="I14" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J14" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="K14" t="n">
         <v>0</v>
       </c>
       <c r="L14" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M14" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="N14" t="n">
-        <v>55</v>
+        <v>42</v>
       </c>
       <c r="O14" t="n">
         <v>1</v>
       </c>
       <c r="P14" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
     </row>
     <row r="15">
@@ -1200,13 +1200,13 @@
         <v>0</v>
       </c>
       <c r="D15" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F15" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G15" t="n">
         <v>0</v>
@@ -1215,25 +1215,25 @@
         <v>0</v>
       </c>
       <c r="I15" t="n">
+        <v>6</v>
+      </c>
+      <c r="J15" t="n">
         <v>3</v>
-      </c>
-      <c r="J15" t="n">
-        <v>1</v>
       </c>
       <c r="K15" t="n">
         <v>0</v>
       </c>
       <c r="L15" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M15" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="N15" t="n">
         <v>0</v>
       </c>
       <c r="O15" t="n">
-        <v>82</v>
+        <v>71</v>
       </c>
       <c r="P15" t="n">
         <v>1</v>
@@ -1246,22 +1246,22 @@
         </is>
       </c>
       <c r="B16" t="n">
+        <v>0</v>
+      </c>
+      <c r="C16" t="n">
+        <v>6</v>
+      </c>
+      <c r="D16" t="n">
         <v>3</v>
       </c>
-      <c r="C16" t="n">
-        <v>5</v>
-      </c>
-      <c r="D16" t="n">
-        <v>2</v>
-      </c>
       <c r="E16" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F16" t="n">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="G16" t="n">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="H16" t="n">
         <v>1</v>
@@ -1273,22 +1273,22 @@
         <v>1</v>
       </c>
       <c r="K16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L16" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="M16" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="N16" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="O16" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="P16" t="n">
-        <v>42</v>
+        <v>65</v>
       </c>
     </row>
   </sheetData>
@@ -1369,7 +1369,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Kitchen</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -1403,7 +1403,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Inside city</t>
+          <t>Tall building</t>
         </is>
       </c>
     </row>
@@ -1454,7 +1454,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Office</t>
         </is>
       </c>
     </row>
@@ -1522,7 +1522,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Office</t>
         </is>
       </c>
     </row>
@@ -1539,7 +1539,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Office</t>
         </is>
       </c>
     </row>
@@ -1556,7 +1556,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Street</t>
+          <t>Bedroom</t>
         </is>
       </c>
     </row>
@@ -1590,7 +1590,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Bedroom</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -1607,7 +1607,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Bedroom</t>
+          <t>Store</t>
         </is>
       </c>
     </row>
@@ -1624,7 +1624,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Bedroom</t>
+          <t>Kitchen</t>
         </is>
       </c>
     </row>
@@ -1641,7 +1641,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Tall building</t>
         </is>
       </c>
     </row>
@@ -1743,7 +1743,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Bedroom</t>
         </is>
       </c>
     </row>
@@ -1777,7 +1777,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Suburb</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -1828,7 +1828,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Bedroom</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -1845,7 +1845,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Kitchen</t>
+          <t>Bedroom</t>
         </is>
       </c>
     </row>
@@ -1913,7 +1913,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Store</t>
+          <t>Forest</t>
         </is>
       </c>
     </row>
@@ -1947,7 +1947,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Office</t>
+          <t>Bedroom</t>
         </is>
       </c>
     </row>
@@ -1981,7 +1981,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Bedroom</t>
         </is>
       </c>
     </row>
@@ -1998,7 +1998,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Bedroom</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -2100,7 +2100,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Kitchen</t>
+          <t>Bedroom</t>
         </is>
       </c>
     </row>
@@ -2134,7 +2134,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Bedroom</t>
+          <t>Inside city</t>
         </is>
       </c>
     </row>
@@ -2236,7 +2236,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Office</t>
         </is>
       </c>
     </row>
@@ -2287,7 +2287,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Inside city</t>
+          <t>Office</t>
         </is>
       </c>
     </row>
@@ -2304,7 +2304,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Bedroom</t>
+          <t>Kitchen</t>
         </is>
       </c>
     </row>
@@ -2338,7 +2338,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Bedroom</t>
         </is>
       </c>
     </row>
@@ -2355,7 +2355,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Store</t>
         </is>
       </c>
     </row>
@@ -2423,7 +2423,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -2474,7 +2474,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Inside city</t>
         </is>
       </c>
     </row>
@@ -2508,7 +2508,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Coast</t>
         </is>
       </c>
     </row>
@@ -2542,7 +2542,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Highway</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -2559,7 +2559,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Bedroom</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -2593,7 +2593,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -2610,7 +2610,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -2678,7 +2678,7 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Inside city</t>
+          <t>Kitchen</t>
         </is>
       </c>
     </row>
@@ -2712,7 +2712,7 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Bedroom</t>
         </is>
       </c>
     </row>
@@ -2746,7 +2746,7 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Kitchen</t>
         </is>
       </c>
     </row>
@@ -2797,7 +2797,7 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Bedroom</t>
+          <t>Coast</t>
         </is>
       </c>
     </row>
@@ -2831,7 +2831,7 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Bedroom</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -2848,7 +2848,7 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Office</t>
         </is>
       </c>
     </row>
@@ -2899,7 +2899,7 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Street</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -2933,7 +2933,7 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Inside city</t>
+          <t>Bedroom</t>
         </is>
       </c>
     </row>
@@ -2950,7 +2950,7 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Suburb</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -3018,7 +3018,7 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Bedroom</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -3052,7 +3052,7 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Mountain</t>
         </is>
       </c>
     </row>
@@ -3069,7 +3069,7 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Highway</t>
         </is>
       </c>
     </row>
@@ -3103,7 +3103,7 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -3137,7 +3137,7 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Suburb</t>
+          <t>Mountain</t>
         </is>
       </c>
     </row>
@@ -3324,7 +3324,7 @@
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Highway</t>
         </is>
       </c>
     </row>
@@ -3426,7 +3426,7 @@
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Forest</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -3443,7 +3443,7 @@
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -3460,7 +3460,7 @@
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Mountain</t>
         </is>
       </c>
     </row>
@@ -3477,7 +3477,7 @@
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -3545,7 +3545,7 @@
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>Highway</t>
+          <t>Coast</t>
         </is>
       </c>
     </row>
@@ -3579,7 +3579,7 @@
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>Mountain</t>
+          <t>Coast</t>
         </is>
       </c>
     </row>
@@ -3596,7 +3596,7 @@
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>Highway</t>
+          <t>Coast</t>
         </is>
       </c>
     </row>
@@ -3630,7 +3630,7 @@
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>Mountain</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -3647,7 +3647,7 @@
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>Forest</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -3681,7 +3681,7 @@
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>Highway</t>
+          <t>Coast</t>
         </is>
       </c>
     </row>
@@ -3715,7 +3715,7 @@
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>Open country</t>
+          <t>Coast</t>
         </is>
       </c>
     </row>
@@ -3749,7 +3749,7 @@
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>Highway</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -3817,7 +3817,7 @@
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Suburb</t>
         </is>
       </c>
     </row>
@@ -3834,7 +3834,7 @@
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>Highway</t>
+          <t>Coast</t>
         </is>
       </c>
     </row>
@@ -3885,7 +3885,7 @@
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Highway</t>
         </is>
       </c>
     </row>
@@ -3919,7 +3919,7 @@
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>Open country</t>
+          <t>Mountain</t>
         </is>
       </c>
     </row>
@@ -3970,7 +3970,7 @@
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>Mountain</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -4089,7 +4089,7 @@
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>Open country</t>
+          <t>Coast</t>
         </is>
       </c>
     </row>
@@ -4106,7 +4106,7 @@
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Mountain</t>
         </is>
       </c>
     </row>
@@ -4140,7 +4140,7 @@
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -4157,7 +4157,7 @@
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>Bedroom</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -4259,7 +4259,7 @@
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Inside city</t>
         </is>
       </c>
     </row>
@@ -4446,7 +4446,7 @@
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Tall building</t>
         </is>
       </c>
     </row>
@@ -4463,7 +4463,7 @@
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Tall building</t>
         </is>
       </c>
     </row>
@@ -4480,7 +4480,7 @@
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>Highway</t>
+          <t>Coast</t>
         </is>
       </c>
     </row>
@@ -4497,7 +4497,7 @@
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t>Open country</t>
+          <t>Coast</t>
         </is>
       </c>
     </row>
@@ -4514,7 +4514,7 @@
       </c>
       <c r="C189" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -4616,7 +4616,7 @@
       </c>
       <c r="C195" t="inlineStr">
         <is>
-          <t>Highway</t>
+          <t>Coast</t>
         </is>
       </c>
     </row>
@@ -4667,7 +4667,7 @@
       </c>
       <c r="C198" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Suburb</t>
         </is>
       </c>
     </row>
@@ -4871,7 +4871,7 @@
       </c>
       <c r="C210" t="inlineStr">
         <is>
-          <t>Suburb</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -4922,7 +4922,7 @@
       </c>
       <c r="C213" t="inlineStr">
         <is>
-          <t>Forest</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -4956,7 +4956,7 @@
       </c>
       <c r="C215" t="inlineStr">
         <is>
-          <t>Forest</t>
+          <t>Mountain</t>
         </is>
       </c>
     </row>
@@ -5160,7 +5160,7 @@
       </c>
       <c r="C227" t="inlineStr">
         <is>
-          <t>Forest</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -5279,7 +5279,7 @@
       </c>
       <c r="C234" t="inlineStr">
         <is>
-          <t>Forest</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -5551,7 +5551,7 @@
       </c>
       <c r="C250" t="inlineStr">
         <is>
-          <t>Forest</t>
+          <t>Mountain</t>
         </is>
       </c>
     </row>
@@ -5568,7 +5568,7 @@
       </c>
       <c r="C251" t="inlineStr">
         <is>
-          <t>Forest</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -5823,7 +5823,7 @@
       </c>
       <c r="C266" t="inlineStr">
         <is>
-          <t>Forest</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -5874,7 +5874,7 @@
       </c>
       <c r="C269" t="inlineStr">
         <is>
-          <t>Forest</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -5942,7 +5942,7 @@
       </c>
       <c r="C273" t="inlineStr">
         <is>
-          <t>Forest</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -5959,7 +5959,7 @@
       </c>
       <c r="C274" t="inlineStr">
         <is>
-          <t>Forest</t>
+          <t>Mountain</t>
         </is>
       </c>
     </row>
@@ -6112,7 +6112,7 @@
       </c>
       <c r="C283" t="inlineStr">
         <is>
-          <t>Forest</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -6282,7 +6282,7 @@
       </c>
       <c r="C293" t="inlineStr">
         <is>
-          <t>Forest</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -6401,7 +6401,7 @@
       </c>
       <c r="C300" t="inlineStr">
         <is>
-          <t>Forest</t>
+          <t>Mountain</t>
         </is>
       </c>
     </row>
@@ -6469,7 +6469,7 @@
       </c>
       <c r="C304" t="inlineStr">
         <is>
-          <t>Street</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -6588,7 +6588,7 @@
       </c>
       <c r="C311" t="inlineStr">
         <is>
-          <t>Highway</t>
+          <t>Coast</t>
         </is>
       </c>
     </row>
@@ -6639,7 +6639,7 @@
       </c>
       <c r="C314" t="inlineStr">
         <is>
-          <t>Inside city</t>
+          <t>Street</t>
         </is>
       </c>
     </row>
@@ -6673,7 +6673,7 @@
       </c>
       <c r="C316" t="inlineStr">
         <is>
-          <t>Highway</t>
+          <t>Coast</t>
         </is>
       </c>
     </row>
@@ -6707,7 +6707,7 @@
       </c>
       <c r="C318" t="inlineStr">
         <is>
-          <t>Highway</t>
+          <t>Suburb</t>
         </is>
       </c>
     </row>
@@ -6792,7 +6792,7 @@
       </c>
       <c r="C323" t="inlineStr">
         <is>
-          <t>Highway</t>
+          <t>Coast</t>
         </is>
       </c>
     </row>
@@ -6877,7 +6877,7 @@
       </c>
       <c r="C328" t="inlineStr">
         <is>
-          <t>Highway</t>
+          <t>Mountain</t>
         </is>
       </c>
     </row>
@@ -6894,7 +6894,7 @@
       </c>
       <c r="C329" t="inlineStr">
         <is>
-          <t>Highway</t>
+          <t>Coast</t>
         </is>
       </c>
     </row>
@@ -6979,7 +6979,7 @@
       </c>
       <c r="C334" t="inlineStr">
         <is>
-          <t>Highway</t>
+          <t>Suburb</t>
         </is>
       </c>
     </row>
@@ -7013,7 +7013,7 @@
       </c>
       <c r="C336" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Highway</t>
         </is>
       </c>
     </row>
@@ -7030,7 +7030,7 @@
       </c>
       <c r="C337" t="inlineStr">
         <is>
-          <t>Highway</t>
+          <t>Coast</t>
         </is>
       </c>
     </row>
@@ -7064,7 +7064,7 @@
       </c>
       <c r="C339" t="inlineStr">
         <is>
-          <t>Highway</t>
+          <t>Coast</t>
         </is>
       </c>
     </row>
@@ -7081,7 +7081,7 @@
       </c>
       <c r="C340" t="inlineStr">
         <is>
-          <t>Suburb</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -7098,7 +7098,7 @@
       </c>
       <c r="C341" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Highway</t>
         </is>
       </c>
     </row>
@@ -7149,7 +7149,7 @@
       </c>
       <c r="C344" t="inlineStr">
         <is>
-          <t>Open country</t>
+          <t>Highway</t>
         </is>
       </c>
     </row>
@@ -7183,7 +7183,7 @@
       </c>
       <c r="C346" t="inlineStr">
         <is>
-          <t>Highway</t>
+          <t>Coast</t>
         </is>
       </c>
     </row>
@@ -7234,7 +7234,7 @@
       </c>
       <c r="C349" t="inlineStr">
         <is>
-          <t>Highway</t>
+          <t>Coast</t>
         </is>
       </c>
     </row>
@@ -7285,7 +7285,7 @@
       </c>
       <c r="C352" t="inlineStr">
         <is>
-          <t>Highway</t>
+          <t>Coast</t>
         </is>
       </c>
     </row>
@@ -7302,7 +7302,7 @@
       </c>
       <c r="C353" t="inlineStr">
         <is>
-          <t>Highway</t>
+          <t>Coast</t>
         </is>
       </c>
     </row>
@@ -7336,7 +7336,7 @@
       </c>
       <c r="C355" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Highway</t>
         </is>
       </c>
     </row>
@@ -7370,7 +7370,7 @@
       </c>
       <c r="C357" t="inlineStr">
         <is>
-          <t>Highway</t>
+          <t>Coast</t>
         </is>
       </c>
     </row>
@@ -7387,7 +7387,7 @@
       </c>
       <c r="C358" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -7421,7 +7421,7 @@
       </c>
       <c r="C360" t="inlineStr">
         <is>
-          <t>Office</t>
+          <t>Store</t>
         </is>
       </c>
     </row>
@@ -7438,7 +7438,7 @@
       </c>
       <c r="C361" t="inlineStr">
         <is>
-          <t>Highway</t>
+          <t>Coast</t>
         </is>
       </c>
     </row>
@@ -7489,7 +7489,7 @@
       </c>
       <c r="C364" t="inlineStr">
         <is>
-          <t>Street</t>
+          <t>Store</t>
         </is>
       </c>
     </row>
@@ -7523,7 +7523,7 @@
       </c>
       <c r="C366" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Highway</t>
         </is>
       </c>
     </row>
@@ -7574,7 +7574,7 @@
       </c>
       <c r="C369" t="inlineStr">
         <is>
-          <t>Bedroom</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -7642,7 +7642,7 @@
       </c>
       <c r="C373" t="inlineStr">
         <is>
-          <t>Highway</t>
+          <t>Tall building</t>
         </is>
       </c>
     </row>
@@ -7659,7 +7659,7 @@
       </c>
       <c r="C374" t="inlineStr">
         <is>
-          <t>Highway</t>
+          <t>Coast</t>
         </is>
       </c>
     </row>
@@ -7693,7 +7693,7 @@
       </c>
       <c r="C376" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Highway</t>
         </is>
       </c>
     </row>
@@ -7710,7 +7710,7 @@
       </c>
       <c r="C377" t="inlineStr">
         <is>
-          <t>Open country</t>
+          <t>Coast</t>
         </is>
       </c>
     </row>
@@ -7744,7 +7744,7 @@
       </c>
       <c r="C379" t="inlineStr">
         <is>
-          <t>Mountain</t>
+          <t>Coast</t>
         </is>
       </c>
     </row>
@@ -7778,7 +7778,7 @@
       </c>
       <c r="C381" t="inlineStr">
         <is>
-          <t>Highway</t>
+          <t>Inside city</t>
         </is>
       </c>
     </row>
@@ -7795,7 +7795,7 @@
       </c>
       <c r="C382" t="inlineStr">
         <is>
-          <t>Kitchen</t>
+          <t>Inside city</t>
         </is>
       </c>
     </row>
@@ -7812,7 +7812,7 @@
       </c>
       <c r="C383" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Tall building</t>
         </is>
       </c>
     </row>
@@ -7829,7 +7829,7 @@
       </c>
       <c r="C384" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Street</t>
         </is>
       </c>
     </row>
@@ -7846,7 +7846,7 @@
       </c>
       <c r="C385" t="inlineStr">
         <is>
-          <t>Highway</t>
+          <t>Coast</t>
         </is>
       </c>
     </row>
@@ -7880,7 +7880,7 @@
       </c>
       <c r="C387" t="inlineStr">
         <is>
-          <t>Highway</t>
+          <t>Tall building</t>
         </is>
       </c>
     </row>
@@ -7897,7 +7897,7 @@
       </c>
       <c r="C388" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Mountain</t>
         </is>
       </c>
     </row>
@@ -7914,7 +7914,7 @@
       </c>
       <c r="C389" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Mountain</t>
         </is>
       </c>
     </row>
@@ -7931,7 +7931,7 @@
       </c>
       <c r="C390" t="inlineStr">
         <is>
-          <t>Highway</t>
+          <t>Coast</t>
         </is>
       </c>
     </row>
@@ -8050,7 +8050,7 @@
       </c>
       <c r="C397" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Tall building</t>
         </is>
       </c>
     </row>
@@ -8084,7 +8084,7 @@
       </c>
       <c r="C399" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Tall building</t>
         </is>
       </c>
     </row>
@@ -8101,7 +8101,7 @@
       </c>
       <c r="C400" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Inside city</t>
         </is>
       </c>
     </row>
@@ -8135,7 +8135,7 @@
       </c>
       <c r="C402" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Tall building</t>
         </is>
       </c>
     </row>
@@ -8152,7 +8152,7 @@
       </c>
       <c r="C403" t="inlineStr">
         <is>
-          <t>Highway</t>
+          <t>Coast</t>
         </is>
       </c>
     </row>
@@ -8169,7 +8169,7 @@
       </c>
       <c r="C404" t="inlineStr">
         <is>
-          <t>Open country</t>
+          <t>Coast</t>
         </is>
       </c>
     </row>
@@ -8220,7 +8220,7 @@
       </c>
       <c r="C407" t="inlineStr">
         <is>
-          <t>Office</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -8254,7 +8254,7 @@
       </c>
       <c r="C409" t="inlineStr">
         <is>
-          <t>Open country</t>
+          <t>Mountain</t>
         </is>
       </c>
     </row>
@@ -8271,7 +8271,7 @@
       </c>
       <c r="C410" t="inlineStr">
         <is>
-          <t>Bedroom</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -8288,7 +8288,7 @@
       </c>
       <c r="C411" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Suburb</t>
         </is>
       </c>
     </row>
@@ -8390,7 +8390,7 @@
       </c>
       <c r="C417" t="inlineStr">
         <is>
-          <t>Street</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -8441,7 +8441,7 @@
       </c>
       <c r="C420" t="inlineStr">
         <is>
-          <t>Suburb</t>
+          <t>Store</t>
         </is>
       </c>
     </row>
@@ -8492,7 +8492,7 @@
       </c>
       <c r="C423" t="inlineStr">
         <is>
-          <t>Street</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -8577,7 +8577,7 @@
       </c>
       <c r="C428" t="inlineStr">
         <is>
-          <t>Street</t>
+          <t>Coast</t>
         </is>
       </c>
     </row>
@@ -8628,7 +8628,7 @@
       </c>
       <c r="C431" t="inlineStr">
         <is>
-          <t>Street</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -8645,7 +8645,7 @@
       </c>
       <c r="C432" t="inlineStr">
         <is>
-          <t>Street</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -8662,7 +8662,7 @@
       </c>
       <c r="C433" t="inlineStr">
         <is>
-          <t>Store</t>
+          <t>Street</t>
         </is>
       </c>
     </row>
@@ -8679,7 +8679,7 @@
       </c>
       <c r="C434" t="inlineStr">
         <is>
-          <t>Street</t>
+          <t>Tall building</t>
         </is>
       </c>
     </row>
@@ -8713,7 +8713,7 @@
       </c>
       <c r="C436" t="inlineStr">
         <is>
-          <t>Bedroom</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -8747,7 +8747,7 @@
       </c>
       <c r="C438" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Street</t>
         </is>
       </c>
     </row>
@@ -8764,7 +8764,7 @@
       </c>
       <c r="C439" t="inlineStr">
         <is>
-          <t>Store</t>
+          <t>Street</t>
         </is>
       </c>
     </row>
@@ -8781,7 +8781,7 @@
       </c>
       <c r="C440" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Inside city</t>
         </is>
       </c>
     </row>
@@ -8832,7 +8832,7 @@
       </c>
       <c r="C443" t="inlineStr">
         <is>
-          <t>Suburb</t>
+          <t>Mountain</t>
         </is>
       </c>
     </row>
@@ -8849,7 +8849,7 @@
       </c>
       <c r="C444" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Street</t>
         </is>
       </c>
     </row>
@@ -8900,7 +8900,7 @@
       </c>
       <c r="C447" t="inlineStr">
         <is>
-          <t>Street</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -8934,7 +8934,7 @@
       </c>
       <c r="C449" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Suburb</t>
         </is>
       </c>
     </row>
@@ -8951,7 +8951,7 @@
       </c>
       <c r="C450" t="inlineStr">
         <is>
-          <t>Store</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -9002,7 +9002,7 @@
       </c>
       <c r="C453" t="inlineStr">
         <is>
-          <t>Bedroom</t>
+          <t>Office</t>
         </is>
       </c>
     </row>
@@ -9019,7 +9019,7 @@
       </c>
       <c r="C454" t="inlineStr">
         <is>
-          <t>Inside city</t>
+          <t>Tall building</t>
         </is>
       </c>
     </row>
@@ -9121,7 +9121,7 @@
       </c>
       <c r="C460" t="inlineStr">
         <is>
-          <t>Street</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -9138,7 +9138,7 @@
       </c>
       <c r="C461" t="inlineStr">
         <is>
-          <t>Store</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -9189,7 +9189,7 @@
       </c>
       <c r="C464" t="inlineStr">
         <is>
-          <t>Street</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -9206,7 +9206,7 @@
       </c>
       <c r="C465" t="inlineStr">
         <is>
-          <t>Street</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -9257,7 +9257,7 @@
       </c>
       <c r="C468" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Tall building</t>
         </is>
       </c>
     </row>
@@ -9274,7 +9274,7 @@
       </c>
       <c r="C469" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Inside city</t>
         </is>
       </c>
     </row>
@@ -9308,7 +9308,7 @@
       </c>
       <c r="C471" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -9325,7 +9325,7 @@
       </c>
       <c r="C472" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Mountain</t>
         </is>
       </c>
     </row>
@@ -9376,7 +9376,7 @@
       </c>
       <c r="C475" t="inlineStr">
         <is>
-          <t>Street</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -9393,7 +9393,7 @@
       </c>
       <c r="C476" t="inlineStr">
         <is>
-          <t>Street</t>
+          <t>Inside city</t>
         </is>
       </c>
     </row>
@@ -9410,7 +9410,7 @@
       </c>
       <c r="C477" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Store</t>
         </is>
       </c>
     </row>
@@ -9427,7 +9427,7 @@
       </c>
       <c r="C478" t="inlineStr">
         <is>
-          <t>Bedroom</t>
+          <t>Coast</t>
         </is>
       </c>
     </row>
@@ -9461,7 +9461,7 @@
       </c>
       <c r="C480" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Inside city</t>
         </is>
       </c>
     </row>
@@ -9478,7 +9478,7 @@
       </c>
       <c r="C481" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Inside city</t>
         </is>
       </c>
     </row>
@@ -9495,7 +9495,7 @@
       </c>
       <c r="C482" t="inlineStr">
         <is>
-          <t>Open country</t>
+          <t>Tall building</t>
         </is>
       </c>
     </row>
@@ -9529,7 +9529,7 @@
       </c>
       <c r="C484" t="inlineStr">
         <is>
-          <t>Store</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -9546,7 +9546,7 @@
       </c>
       <c r="C485" t="inlineStr">
         <is>
-          <t>Street</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -9563,7 +9563,7 @@
       </c>
       <c r="C486" t="inlineStr">
         <is>
-          <t>Highway</t>
+          <t>Coast</t>
         </is>
       </c>
     </row>
@@ -9631,7 +9631,7 @@
       </c>
       <c r="C490" t="inlineStr">
         <is>
-          <t>Inside city</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -9648,7 +9648,7 @@
       </c>
       <c r="C491" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Tall building</t>
         </is>
       </c>
     </row>
@@ -9665,7 +9665,7 @@
       </c>
       <c r="C492" t="inlineStr">
         <is>
-          <t>Bedroom</t>
+          <t>Inside city</t>
         </is>
       </c>
     </row>
@@ -9733,7 +9733,7 @@
       </c>
       <c r="C496" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Tall building</t>
         </is>
       </c>
     </row>
@@ -9750,7 +9750,7 @@
       </c>
       <c r="C497" t="inlineStr">
         <is>
-          <t>Suburb</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -9784,7 +9784,7 @@
       </c>
       <c r="C499" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Kitchen</t>
         </is>
       </c>
     </row>
@@ -9852,7 +9852,7 @@
       </c>
       <c r="C503" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Inside city</t>
         </is>
       </c>
     </row>
@@ -9886,7 +9886,7 @@
       </c>
       <c r="C505" t="inlineStr">
         <is>
-          <t>Inside city</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -9903,7 +9903,7 @@
       </c>
       <c r="C506" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -9988,7 +9988,7 @@
       </c>
       <c r="C511" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Tall building</t>
         </is>
       </c>
     </row>
@@ -10005,7 +10005,7 @@
       </c>
       <c r="C512" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Inside city</t>
         </is>
       </c>
     </row>
@@ -10039,7 +10039,7 @@
       </c>
       <c r="C514" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Inside city</t>
         </is>
       </c>
     </row>
@@ -10124,7 +10124,7 @@
       </c>
       <c r="C519" t="inlineStr">
         <is>
-          <t>Suburb</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -10158,7 +10158,7 @@
       </c>
       <c r="C521" t="inlineStr">
         <is>
-          <t>Office</t>
+          <t>Inside city</t>
         </is>
       </c>
     </row>
@@ -10209,7 +10209,7 @@
       </c>
       <c r="C524" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Inside city</t>
         </is>
       </c>
     </row>
@@ -10243,7 +10243,7 @@
       </c>
       <c r="C526" t="inlineStr">
         <is>
-          <t>Street</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -10345,7 +10345,7 @@
       </c>
       <c r="C532" t="inlineStr">
         <is>
-          <t>Kitchen</t>
+          <t>Inside city</t>
         </is>
       </c>
     </row>
@@ -10362,7 +10362,7 @@
       </c>
       <c r="C533" t="inlineStr">
         <is>
-          <t>Inside city</t>
+          <t>Tall building</t>
         </is>
       </c>
     </row>
@@ -10498,7 +10498,7 @@
       </c>
       <c r="C541" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Inside city</t>
         </is>
       </c>
     </row>
@@ -10515,7 +10515,7 @@
       </c>
       <c r="C542" t="inlineStr">
         <is>
-          <t>Store</t>
+          <t>Street</t>
         </is>
       </c>
     </row>
@@ -10532,7 +10532,7 @@
       </c>
       <c r="C543" t="inlineStr">
         <is>
-          <t>Store</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -10583,7 +10583,7 @@
       </c>
       <c r="C546" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Inside city</t>
         </is>
       </c>
     </row>
@@ -10600,7 +10600,7 @@
       </c>
       <c r="C547" t="inlineStr">
         <is>
-          <t>Inside city</t>
+          <t>Tall building</t>
         </is>
       </c>
     </row>
@@ -10617,7 +10617,7 @@
       </c>
       <c r="C548" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Inside city</t>
         </is>
       </c>
     </row>
@@ -10685,7 +10685,7 @@
       </c>
       <c r="C552" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Inside city</t>
         </is>
       </c>
     </row>
@@ -10702,7 +10702,7 @@
       </c>
       <c r="C553" t="inlineStr">
         <is>
-          <t>Inside city</t>
+          <t>Bedroom</t>
         </is>
       </c>
     </row>
@@ -10719,7 +10719,7 @@
       </c>
       <c r="C554" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Inside city</t>
         </is>
       </c>
     </row>
@@ -10787,7 +10787,7 @@
       </c>
       <c r="C558" t="inlineStr">
         <is>
-          <t>Inside city</t>
+          <t>Store</t>
         </is>
       </c>
     </row>
@@ -10804,7 +10804,7 @@
       </c>
       <c r="C559" t="inlineStr">
         <is>
-          <t>Street</t>
+          <t>Tall building</t>
         </is>
       </c>
     </row>
@@ -10889,7 +10889,7 @@
       </c>
       <c r="C564" t="inlineStr">
         <is>
-          <t>Street</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -10923,7 +10923,7 @@
       </c>
       <c r="C566" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Inside city</t>
         </is>
       </c>
     </row>
@@ -11008,7 +11008,7 @@
       </c>
       <c r="C571" t="inlineStr">
         <is>
-          <t>Street</t>
+          <t>Mountain</t>
         </is>
       </c>
     </row>
@@ -11025,7 +11025,7 @@
       </c>
       <c r="C572" t="inlineStr">
         <is>
-          <t>Street</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -11042,7 +11042,7 @@
       </c>
       <c r="C573" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Inside city</t>
         </is>
       </c>
     </row>
@@ -11110,7 +11110,7 @@
       </c>
       <c r="C577" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Inside city</t>
         </is>
       </c>
     </row>
@@ -11144,7 +11144,7 @@
       </c>
       <c r="C579" t="inlineStr">
         <is>
-          <t>Street</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -11161,7 +11161,7 @@
       </c>
       <c r="C580" t="inlineStr">
         <is>
-          <t>Inside city</t>
+          <t>Tall building</t>
         </is>
       </c>
     </row>
@@ -11212,7 +11212,7 @@
       </c>
       <c r="C583" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Tall building</t>
         </is>
       </c>
     </row>
@@ -11246,7 +11246,7 @@
       </c>
       <c r="C585" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Inside city</t>
         </is>
       </c>
     </row>
@@ -11280,7 +11280,7 @@
       </c>
       <c r="C587" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Inside city</t>
         </is>
       </c>
     </row>
@@ -11314,7 +11314,7 @@
       </c>
       <c r="C589" t="inlineStr">
         <is>
-          <t>Inside city</t>
+          <t>Store</t>
         </is>
       </c>
     </row>
@@ -11348,7 +11348,7 @@
       </c>
       <c r="C591" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Highway</t>
         </is>
       </c>
     </row>
@@ -11365,7 +11365,7 @@
       </c>
       <c r="C592" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Inside city</t>
         </is>
       </c>
     </row>
@@ -11382,7 +11382,7 @@
       </c>
       <c r="C593" t="inlineStr">
         <is>
-          <t>Inside city</t>
+          <t>Tall building</t>
         </is>
       </c>
     </row>
@@ -11399,7 +11399,7 @@
       </c>
       <c r="C594" t="inlineStr">
         <is>
-          <t>Bedroom</t>
+          <t>Mountain</t>
         </is>
       </c>
     </row>
@@ -11416,7 +11416,7 @@
       </c>
       <c r="C595" t="inlineStr">
         <is>
-          <t>Inside city</t>
+          <t>Store</t>
         </is>
       </c>
     </row>
@@ -11501,7 +11501,7 @@
       </c>
       <c r="C600" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Office</t>
         </is>
       </c>
     </row>
@@ -11518,7 +11518,7 @@
       </c>
       <c r="C601" t="inlineStr">
         <is>
-          <t>Inside city</t>
+          <t>Tall building</t>
         </is>
       </c>
     </row>
@@ -11535,7 +11535,7 @@
       </c>
       <c r="C602" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Inside city</t>
         </is>
       </c>
     </row>
@@ -11552,7 +11552,7 @@
       </c>
       <c r="C603" t="inlineStr">
         <is>
-          <t>Inside city</t>
+          <t>Kitchen</t>
         </is>
       </c>
     </row>
@@ -11569,7 +11569,7 @@
       </c>
       <c r="C604" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Suburb</t>
         </is>
       </c>
     </row>
@@ -11586,7 +11586,7 @@
       </c>
       <c r="C605" t="inlineStr">
         <is>
-          <t>Kitchen</t>
+          <t>Bedroom</t>
         </is>
       </c>
     </row>
@@ -11620,7 +11620,7 @@
       </c>
       <c r="C607" t="inlineStr">
         <is>
-          <t>Inside city</t>
+          <t>Kitchen</t>
         </is>
       </c>
     </row>
@@ -11637,7 +11637,7 @@
       </c>
       <c r="C608" t="inlineStr">
         <is>
-          <t>Inside city</t>
+          <t>Street</t>
         </is>
       </c>
     </row>
@@ -11671,7 +11671,7 @@
       </c>
       <c r="C610" t="inlineStr">
         <is>
-          <t>Bedroom</t>
+          <t>Kitchen</t>
         </is>
       </c>
     </row>
@@ -11688,7 +11688,7 @@
       </c>
       <c r="C611" t="inlineStr">
         <is>
-          <t>Office</t>
+          <t>Inside city</t>
         </is>
       </c>
     </row>
@@ -11705,7 +11705,7 @@
       </c>
       <c r="C612" t="inlineStr">
         <is>
-          <t>Office</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -11722,7 +11722,7 @@
       </c>
       <c r="C613" t="inlineStr">
         <is>
-          <t>Office</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -11739,7 +11739,7 @@
       </c>
       <c r="C614" t="inlineStr">
         <is>
-          <t>Office</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -11824,7 +11824,7 @@
       </c>
       <c r="C619" t="inlineStr">
         <is>
-          <t>Bedroom</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -11841,7 +11841,7 @@
       </c>
       <c r="C620" t="inlineStr">
         <is>
-          <t>Store</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -11858,7 +11858,7 @@
       </c>
       <c r="C621" t="inlineStr">
         <is>
-          <t>Bedroom</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -11875,7 +11875,7 @@
       </c>
       <c r="C622" t="inlineStr">
         <is>
-          <t>Office</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -11926,7 +11926,7 @@
       </c>
       <c r="C625" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -11960,7 +11960,7 @@
       </c>
       <c r="C627" t="inlineStr">
         <is>
-          <t>Inside city</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -11994,7 +11994,7 @@
       </c>
       <c r="C629" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Inside city</t>
         </is>
       </c>
     </row>
@@ -12028,7 +12028,7 @@
       </c>
       <c r="C631" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Inside city</t>
         </is>
       </c>
     </row>
@@ -12062,7 +12062,7 @@
       </c>
       <c r="C633" t="inlineStr">
         <is>
-          <t>Office</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -12079,7 +12079,7 @@
       </c>
       <c r="C634" t="inlineStr">
         <is>
-          <t>Tall building</t>
+          <t>Store</t>
         </is>
       </c>
     </row>
@@ -12130,7 +12130,7 @@
       </c>
       <c r="C637" t="inlineStr">
         <is>
-          <t>Office</t>
+          <t>Kitchen</t>
         </is>
       </c>
     </row>
@@ -12181,7 +12181,7 @@
       </c>
       <c r="C640" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -12198,7 +12198,7 @@
       </c>
       <c r="C641" t="inlineStr">
         <is>
-          <t>Bedroom</t>
+          <t>Kitchen</t>
         </is>
       </c>
     </row>
@@ -12266,7 +12266,7 @@
       </c>
       <c r="C645" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Inside city</t>
         </is>
       </c>
     </row>
@@ -12317,7 +12317,7 @@
       </c>
       <c r="C648" t="inlineStr">
         <is>
-          <t>Street</t>
+          <t>Store</t>
         </is>
       </c>
     </row>
@@ -12334,7 +12334,7 @@
       </c>
       <c r="C649" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -12351,7 +12351,7 @@
       </c>
       <c r="C650" t="inlineStr">
         <is>
-          <t>Office</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -12402,7 +12402,7 @@
       </c>
       <c r="C653" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Office</t>
         </is>
       </c>
     </row>
@@ -12436,7 +12436,7 @@
       </c>
       <c r="C655" t="inlineStr">
         <is>
-          <t>Kitchen</t>
+          <t>Inside city</t>
         </is>
       </c>
     </row>
@@ -12453,7 +12453,7 @@
       </c>
       <c r="C656" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Kitchen</t>
         </is>
       </c>
     </row>
@@ -12470,7 +12470,7 @@
       </c>
       <c r="C657" t="inlineStr">
         <is>
-          <t>Kitchen</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -12487,7 +12487,7 @@
       </c>
       <c r="C658" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -12504,7 +12504,7 @@
       </c>
       <c r="C659" t="inlineStr">
         <is>
-          <t>Bedroom</t>
+          <t>Kitchen</t>
         </is>
       </c>
     </row>
@@ -12555,7 +12555,7 @@
       </c>
       <c r="C662" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Store</t>
         </is>
       </c>
     </row>
@@ -12572,7 +12572,7 @@
       </c>
       <c r="C663" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -12589,7 +12589,7 @@
       </c>
       <c r="C664" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Store</t>
         </is>
       </c>
     </row>
@@ -12623,7 +12623,7 @@
       </c>
       <c r="C666" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -12640,7 +12640,7 @@
       </c>
       <c r="C667" t="inlineStr">
         <is>
-          <t>Office</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -12657,7 +12657,7 @@
       </c>
       <c r="C668" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Inside city</t>
         </is>
       </c>
     </row>
@@ -12674,7 +12674,7 @@
       </c>
       <c r="C669" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Office</t>
         </is>
       </c>
     </row>
@@ -12691,7 +12691,7 @@
       </c>
       <c r="C670" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Bedroom</t>
         </is>
       </c>
     </row>
@@ -12725,7 +12725,7 @@
       </c>
       <c r="C672" t="inlineStr">
         <is>
-          <t>Kitchen</t>
+          <t>Store</t>
         </is>
       </c>
     </row>
@@ -12827,7 +12827,7 @@
       </c>
       <c r="C678" t="inlineStr">
         <is>
-          <t>Store</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -12912,7 +12912,7 @@
       </c>
       <c r="C683" t="inlineStr">
         <is>
-          <t>Office</t>
+          <t>Highway</t>
         </is>
       </c>
     </row>
@@ -12963,7 +12963,7 @@
       </c>
       <c r="C686" t="inlineStr">
         <is>
-          <t>Inside city</t>
+          <t>Tall building</t>
         </is>
       </c>
     </row>
@@ -12980,7 +12980,7 @@
       </c>
       <c r="C687" t="inlineStr">
         <is>
-          <t>Bedroom</t>
+          <t>Kitchen</t>
         </is>
       </c>
     </row>
@@ -12997,7 +12997,7 @@
       </c>
       <c r="C688" t="inlineStr">
         <is>
-          <t>Office</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -13014,7 +13014,7 @@
       </c>
       <c r="C689" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Store</t>
         </is>
       </c>
     </row>
@@ -13031,7 +13031,7 @@
       </c>
       <c r="C690" t="inlineStr">
         <is>
-          <t>Bedroom</t>
+          <t>Kitchen</t>
         </is>
       </c>
     </row>
@@ -13048,7 +13048,7 @@
       </c>
       <c r="C691" t="inlineStr">
         <is>
-          <t>Inside city</t>
+          <t>Kitchen</t>
         </is>
       </c>
     </row>
@@ -13116,7 +13116,7 @@
       </c>
       <c r="C695" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Office</t>
         </is>
       </c>
     </row>
@@ -13150,7 +13150,7 @@
       </c>
       <c r="C697" t="inlineStr">
         <is>
-          <t>Store</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -13184,7 +13184,7 @@
       </c>
       <c r="C699" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Bedroom</t>
         </is>
       </c>
     </row>
@@ -13201,7 +13201,7 @@
       </c>
       <c r="C700" t="inlineStr">
         <is>
-          <t>Office</t>
+          <t>Inside city</t>
         </is>
       </c>
     </row>
@@ -13218,7 +13218,7 @@
       </c>
       <c r="C701" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -13235,7 +13235,7 @@
       </c>
       <c r="C702" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Suburb</t>
         </is>
       </c>
     </row>
@@ -13252,7 +13252,7 @@
       </c>
       <c r="C703" t="inlineStr">
         <is>
-          <t>Kitchen</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -13269,7 +13269,7 @@
       </c>
       <c r="C704" t="inlineStr">
         <is>
-          <t>Office</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -13286,7 +13286,7 @@
       </c>
       <c r="C705" t="inlineStr">
         <is>
-          <t>Store</t>
+          <t>Street</t>
         </is>
       </c>
     </row>
@@ -13320,7 +13320,7 @@
       </c>
       <c r="C707" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -13337,7 +13337,7 @@
       </c>
       <c r="C708" t="inlineStr">
         <is>
-          <t>Office</t>
+          <t>Store</t>
         </is>
       </c>
     </row>
@@ -13354,7 +13354,7 @@
       </c>
       <c r="C709" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Kitchen</t>
         </is>
       </c>
     </row>
@@ -13371,7 +13371,7 @@
       </c>
       <c r="C710" t="inlineStr">
         <is>
-          <t>Office</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -13405,7 +13405,7 @@
       </c>
       <c r="C712" t="inlineStr">
         <is>
-          <t>Office</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -13558,7 +13558,7 @@
       </c>
       <c r="C721" t="inlineStr">
         <is>
-          <t>Office</t>
+          <t>Suburb</t>
         </is>
       </c>
     </row>
@@ -13575,7 +13575,7 @@
       </c>
       <c r="C722" t="inlineStr">
         <is>
-          <t>Tall building</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -13592,7 +13592,7 @@
       </c>
       <c r="C723" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -13643,7 +13643,7 @@
       </c>
       <c r="C726" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Office</t>
         </is>
       </c>
     </row>
@@ -13660,7 +13660,7 @@
       </c>
       <c r="C727" t="inlineStr">
         <is>
-          <t>Office</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -13728,7 +13728,7 @@
       </c>
       <c r="C731" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Bedroom</t>
         </is>
       </c>
     </row>
@@ -13830,7 +13830,7 @@
       </c>
       <c r="C737" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -13898,7 +13898,7 @@
       </c>
       <c r="C741" t="inlineStr">
         <is>
-          <t>Office</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -13932,7 +13932,7 @@
       </c>
       <c r="C743" t="inlineStr">
         <is>
-          <t>Store</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -13966,7 +13966,7 @@
       </c>
       <c r="C745" t="inlineStr">
         <is>
-          <t>Bedroom</t>
+          <t>Tall building</t>
         </is>
       </c>
     </row>
@@ -14017,7 +14017,7 @@
       </c>
       <c r="C748" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Inside city</t>
         </is>
       </c>
     </row>
@@ -14085,7 +14085,7 @@
       </c>
       <c r="C752" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Bedroom</t>
         </is>
       </c>
     </row>
@@ -14102,7 +14102,7 @@
       </c>
       <c r="C753" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Bedroom</t>
         </is>
       </c>
     </row>
@@ -14153,7 +14153,7 @@
       </c>
       <c r="C756" t="inlineStr">
         <is>
-          <t>Bedroom</t>
+          <t>Kitchen</t>
         </is>
       </c>
     </row>
@@ -14170,7 +14170,7 @@
       </c>
       <c r="C757" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Store</t>
         </is>
       </c>
     </row>
@@ -14204,7 +14204,7 @@
       </c>
       <c r="C759" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Store</t>
         </is>
       </c>
     </row>
@@ -14221,7 +14221,7 @@
       </c>
       <c r="C760" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Bedroom</t>
         </is>
       </c>
     </row>
@@ -14323,7 +14323,7 @@
       </c>
       <c r="C766" t="inlineStr">
         <is>
-          <t>Store</t>
+          <t>Tall building</t>
         </is>
       </c>
     </row>
@@ -14374,7 +14374,7 @@
       </c>
       <c r="C769" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Office</t>
         </is>
       </c>
     </row>
@@ -14391,7 +14391,7 @@
       </c>
       <c r="C770" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Kitchen</t>
         </is>
       </c>
     </row>
@@ -14425,7 +14425,7 @@
       </c>
       <c r="C772" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -14442,7 +14442,7 @@
       </c>
       <c r="C773" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Suburb</t>
         </is>
       </c>
     </row>
@@ -14459,7 +14459,7 @@
       </c>
       <c r="C774" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -14510,7 +14510,7 @@
       </c>
       <c r="C777" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -14527,7 +14527,7 @@
       </c>
       <c r="C778" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -14578,7 +14578,7 @@
       </c>
       <c r="C781" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Tall building</t>
         </is>
       </c>
     </row>
@@ -14629,7 +14629,7 @@
       </c>
       <c r="C784" t="inlineStr">
         <is>
-          <t>Office</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -14663,7 +14663,7 @@
       </c>
       <c r="C786" t="inlineStr">
         <is>
-          <t>Bedroom</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -14680,7 +14680,7 @@
       </c>
       <c r="C787" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Office</t>
         </is>
       </c>
     </row>
@@ -14714,7 +14714,7 @@
       </c>
       <c r="C789" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Store</t>
         </is>
       </c>
     </row>
@@ -14765,7 +14765,7 @@
       </c>
       <c r="C792" t="inlineStr">
         <is>
-          <t>Bedroom</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -14782,7 +14782,7 @@
       </c>
       <c r="C793" t="inlineStr">
         <is>
-          <t>Highway</t>
+          <t>Forest</t>
         </is>
       </c>
     </row>
@@ -14816,7 +14816,7 @@
       </c>
       <c r="C795" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Store</t>
         </is>
       </c>
     </row>
@@ -14833,7 +14833,7 @@
       </c>
       <c r="C796" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Street</t>
         </is>
       </c>
     </row>
@@ -14867,7 +14867,7 @@
       </c>
       <c r="C798" t="inlineStr">
         <is>
-          <t>Bedroom</t>
+          <t>Kitchen</t>
         </is>
       </c>
     </row>
@@ -14901,7 +14901,7 @@
       </c>
       <c r="C800" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Store</t>
         </is>
       </c>
     </row>
@@ -14918,7 +14918,7 @@
       </c>
       <c r="C801" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -14952,7 +14952,7 @@
       </c>
       <c r="C803" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -14969,7 +14969,7 @@
       </c>
       <c r="C804" t="inlineStr">
         <is>
-          <t>Forest</t>
+          <t>Mountain</t>
         </is>
       </c>
     </row>
@@ -14986,7 +14986,7 @@
       </c>
       <c r="C805" t="inlineStr">
         <is>
-          <t>Forest</t>
+          <t>Mountain</t>
         </is>
       </c>
     </row>
@@ -15020,7 +15020,7 @@
       </c>
       <c r="C807" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -15037,7 +15037,7 @@
       </c>
       <c r="C808" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Mountain</t>
         </is>
       </c>
     </row>
@@ -15054,7 +15054,7 @@
       </c>
       <c r="C809" t="inlineStr">
         <is>
-          <t>Forest</t>
+          <t>Mountain</t>
         </is>
       </c>
     </row>
@@ -15071,7 +15071,7 @@
       </c>
       <c r="C810" t="inlineStr">
         <is>
-          <t>Open country</t>
+          <t>Mountain</t>
         </is>
       </c>
     </row>
@@ -15105,7 +15105,7 @@
       </c>
       <c r="C812" t="inlineStr">
         <is>
-          <t>Open country</t>
+          <t>Mountain</t>
         </is>
       </c>
     </row>
@@ -15122,7 +15122,7 @@
       </c>
       <c r="C813" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Mountain</t>
         </is>
       </c>
     </row>
@@ -15207,7 +15207,7 @@
       </c>
       <c r="C818" t="inlineStr">
         <is>
-          <t>Suburb</t>
+          <t>Mountain</t>
         </is>
       </c>
     </row>
@@ -15394,7 +15394,7 @@
       </c>
       <c r="C829" t="inlineStr">
         <is>
-          <t>Mountain</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -15513,7 +15513,7 @@
       </c>
       <c r="C836" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -15615,7 +15615,7 @@
       </c>
       <c r="C842" t="inlineStr">
         <is>
-          <t>Forest</t>
+          <t>Mountain</t>
         </is>
       </c>
     </row>
@@ -15666,7 +15666,7 @@
       </c>
       <c r="C845" t="inlineStr">
         <is>
-          <t>Highway</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -15700,7 +15700,7 @@
       </c>
       <c r="C847" t="inlineStr">
         <is>
-          <t>Forest</t>
+          <t>Mountain</t>
         </is>
       </c>
     </row>
@@ -15717,7 +15717,7 @@
       </c>
       <c r="C848" t="inlineStr">
         <is>
-          <t>Open country</t>
+          <t>Mountain</t>
         </is>
       </c>
     </row>
@@ -15802,7 +15802,7 @@
       </c>
       <c r="C853" t="inlineStr">
         <is>
-          <t>Forest</t>
+          <t>Mountain</t>
         </is>
       </c>
     </row>
@@ -15819,7 +15819,7 @@
       </c>
       <c r="C854" t="inlineStr">
         <is>
-          <t>Mountain</t>
+          <t>Street</t>
         </is>
       </c>
     </row>
@@ -15870,7 +15870,7 @@
       </c>
       <c r="C857" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Mountain</t>
         </is>
       </c>
     </row>
@@ -15921,7 +15921,7 @@
       </c>
       <c r="C860" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Mountain</t>
         </is>
       </c>
     </row>
@@ -16006,7 +16006,7 @@
       </c>
       <c r="C865" t="inlineStr">
         <is>
-          <t>Open country</t>
+          <t>Mountain</t>
         </is>
       </c>
     </row>
@@ -16023,7 +16023,7 @@
       </c>
       <c r="C866" t="inlineStr">
         <is>
-          <t>Mountain</t>
+          <t>Coast</t>
         </is>
       </c>
     </row>
@@ -16057,7 +16057,7 @@
       </c>
       <c r="C868" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -16091,7 +16091,7 @@
       </c>
       <c r="C870" t="inlineStr">
         <is>
-          <t>Open country</t>
+          <t>Mountain</t>
         </is>
       </c>
     </row>
@@ -16108,7 +16108,7 @@
       </c>
       <c r="C871" t="inlineStr">
         <is>
-          <t>Forest</t>
+          <t>Mountain</t>
         </is>
       </c>
     </row>
@@ -16176,7 +16176,7 @@
       </c>
       <c r="C875" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Mountain</t>
         </is>
       </c>
     </row>
@@ -16193,7 +16193,7 @@
       </c>
       <c r="C876" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Mountain</t>
         </is>
       </c>
     </row>
@@ -16210,7 +16210,7 @@
       </c>
       <c r="C877" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Mountain</t>
         </is>
       </c>
     </row>
@@ -16261,7 +16261,7 @@
       </c>
       <c r="C880" t="inlineStr">
         <is>
-          <t>Forest</t>
+          <t>Mountain</t>
         </is>
       </c>
     </row>
@@ -16278,7 +16278,7 @@
       </c>
       <c r="C881" t="inlineStr">
         <is>
-          <t>Forest</t>
+          <t>Mountain</t>
         </is>
       </c>
     </row>
@@ -16312,7 +16312,7 @@
       </c>
       <c r="C883" t="inlineStr">
         <is>
-          <t>Forest</t>
+          <t>Mountain</t>
         </is>
       </c>
     </row>
@@ -16346,7 +16346,7 @@
       </c>
       <c r="C885" t="inlineStr">
         <is>
-          <t>Forest</t>
+          <t>Mountain</t>
         </is>
       </c>
     </row>
@@ -16363,7 +16363,7 @@
       </c>
       <c r="C886" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Mountain</t>
         </is>
       </c>
     </row>
@@ -16397,7 +16397,7 @@
       </c>
       <c r="C888" t="inlineStr">
         <is>
-          <t>Mountain</t>
+          <t>Coast</t>
         </is>
       </c>
     </row>
@@ -16431,7 +16431,7 @@
       </c>
       <c r="C890" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Street</t>
         </is>
       </c>
     </row>
@@ -16465,7 +16465,7 @@
       </c>
       <c r="C892" t="inlineStr">
         <is>
-          <t>Street</t>
+          <t>Mountain</t>
         </is>
       </c>
     </row>
@@ -16482,7 +16482,7 @@
       </c>
       <c r="C893" t="inlineStr">
         <is>
-          <t>Mountain</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -16499,7 +16499,7 @@
       </c>
       <c r="C894" t="inlineStr">
         <is>
-          <t>Forest</t>
+          <t>Mountain</t>
         </is>
       </c>
     </row>
@@ -16533,7 +16533,7 @@
       </c>
       <c r="C896" t="inlineStr">
         <is>
-          <t>Forest</t>
+          <t>Mountain</t>
         </is>
       </c>
     </row>
@@ -16567,7 +16567,7 @@
       </c>
       <c r="C898" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Mountain</t>
         </is>
       </c>
     </row>
@@ -16584,7 +16584,7 @@
       </c>
       <c r="C899" t="inlineStr">
         <is>
-          <t>Forest</t>
+          <t>Mountain</t>
         </is>
       </c>
     </row>
@@ -16601,7 +16601,7 @@
       </c>
       <c r="C900" t="inlineStr">
         <is>
-          <t>Forest</t>
+          <t>Mountain</t>
         </is>
       </c>
     </row>
@@ -16635,7 +16635,7 @@
       </c>
       <c r="C902" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Inside city</t>
         </is>
       </c>
     </row>
@@ -16652,7 +16652,7 @@
       </c>
       <c r="C903" t="inlineStr">
         <is>
-          <t>Office</t>
+          <t>Street</t>
         </is>
       </c>
     </row>
@@ -16771,7 +16771,7 @@
       </c>
       <c r="C910" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Office</t>
         </is>
       </c>
     </row>
@@ -16805,7 +16805,7 @@
       </c>
       <c r="C912" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -16856,7 +16856,7 @@
       </c>
       <c r="C915" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Tall building</t>
         </is>
       </c>
     </row>
@@ -16873,7 +16873,7 @@
       </c>
       <c r="C916" t="inlineStr">
         <is>
-          <t>Office</t>
+          <t>Inside city</t>
         </is>
       </c>
     </row>
@@ -16890,7 +16890,7 @@
       </c>
       <c r="C917" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Office</t>
         </is>
       </c>
     </row>
@@ -16958,7 +16958,7 @@
       </c>
       <c r="C921" t="inlineStr">
         <is>
-          <t>Store</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -17060,7 +17060,7 @@
       </c>
       <c r="C927" t="inlineStr">
         <is>
-          <t>Office</t>
+          <t>Inside city</t>
         </is>
       </c>
     </row>
@@ -17094,7 +17094,7 @@
       </c>
       <c r="C929" t="inlineStr">
         <is>
-          <t>Office</t>
+          <t>Bedroom</t>
         </is>
       </c>
     </row>
@@ -17128,7 +17128,7 @@
       </c>
       <c r="C931" t="inlineStr">
         <is>
-          <t>Office</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -17196,7 +17196,7 @@
       </c>
       <c r="C935" t="inlineStr">
         <is>
-          <t>Office</t>
+          <t>Inside city</t>
         </is>
       </c>
     </row>
@@ -17213,7 +17213,7 @@
       </c>
       <c r="C936" t="inlineStr">
         <is>
-          <t>Inside city</t>
+          <t>Bedroom</t>
         </is>
       </c>
     </row>
@@ -17230,7 +17230,7 @@
       </c>
       <c r="C937" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Office</t>
         </is>
       </c>
     </row>
@@ -17247,7 +17247,7 @@
       </c>
       <c r="C938" t="inlineStr">
         <is>
-          <t>Office</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -17264,7 +17264,7 @@
       </c>
       <c r="C939" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Office</t>
         </is>
       </c>
     </row>
@@ -17298,7 +17298,7 @@
       </c>
       <c r="C941" t="inlineStr">
         <is>
-          <t>Office</t>
+          <t>Inside city</t>
         </is>
       </c>
     </row>
@@ -17383,7 +17383,7 @@
       </c>
       <c r="C946" t="inlineStr">
         <is>
-          <t>Office</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -17434,7 +17434,7 @@
       </c>
       <c r="C949" t="inlineStr">
         <is>
-          <t>Street</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -17519,7 +17519,7 @@
       </c>
       <c r="C954" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Store</t>
         </is>
       </c>
     </row>
@@ -17536,7 +17536,7 @@
       </c>
       <c r="C955" t="inlineStr">
         <is>
-          <t>Kitchen</t>
+          <t>Office</t>
         </is>
       </c>
     </row>
@@ -17570,7 +17570,7 @@
       </c>
       <c r="C957" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Office</t>
         </is>
       </c>
     </row>
@@ -17587,7 +17587,7 @@
       </c>
       <c r="C958" t="inlineStr">
         <is>
-          <t>Office</t>
+          <t>Store</t>
         </is>
       </c>
     </row>
@@ -17638,7 +17638,7 @@
       </c>
       <c r="C961" t="inlineStr">
         <is>
-          <t>Office</t>
+          <t>Inside city</t>
         </is>
       </c>
     </row>
@@ -17655,7 +17655,7 @@
       </c>
       <c r="C962" t="inlineStr">
         <is>
-          <t>Store</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -17672,7 +17672,7 @@
       </c>
       <c r="C963" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Inside city</t>
         </is>
       </c>
     </row>
@@ -17706,7 +17706,7 @@
       </c>
       <c r="C965" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Office</t>
         </is>
       </c>
     </row>
@@ -17740,7 +17740,7 @@
       </c>
       <c r="C967" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Office</t>
         </is>
       </c>
     </row>
@@ -17757,7 +17757,7 @@
       </c>
       <c r="C968" t="inlineStr">
         <is>
-          <t>Office</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -17791,7 +17791,7 @@
       </c>
       <c r="C970" t="inlineStr">
         <is>
-          <t>Office</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -17842,7 +17842,7 @@
       </c>
       <c r="C973" t="inlineStr">
         <is>
-          <t>Office</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -17910,7 +17910,7 @@
       </c>
       <c r="C977" t="inlineStr">
         <is>
-          <t>Office</t>
+          <t>Inside city</t>
         </is>
       </c>
     </row>
@@ -17961,7 +17961,7 @@
       </c>
       <c r="C980" t="inlineStr">
         <is>
-          <t>Office</t>
+          <t>Kitchen</t>
         </is>
       </c>
     </row>
@@ -18063,7 +18063,7 @@
       </c>
       <c r="C986" t="inlineStr">
         <is>
-          <t>Kitchen</t>
+          <t>Inside city</t>
         </is>
       </c>
     </row>
@@ -18114,7 +18114,7 @@
       </c>
       <c r="C989" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Office</t>
         </is>
       </c>
     </row>
@@ -18148,7 +18148,7 @@
       </c>
       <c r="C991" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Office</t>
         </is>
       </c>
     </row>
@@ -18301,7 +18301,7 @@
       </c>
       <c r="C1000" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Suburb</t>
         </is>
       </c>
     </row>
@@ -18318,7 +18318,7 @@
       </c>
       <c r="C1001" t="inlineStr">
         <is>
-          <t>Office</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -18335,7 +18335,7 @@
       </c>
       <c r="C1002" t="inlineStr">
         <is>
-          <t>Highway</t>
+          <t>Mountain</t>
         </is>
       </c>
     </row>
@@ -18369,7 +18369,7 @@
       </c>
       <c r="C1004" t="inlineStr">
         <is>
-          <t>Mountain</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -18420,7 +18420,7 @@
       </c>
       <c r="C1007" t="inlineStr">
         <is>
-          <t>Forest</t>
+          <t>Mountain</t>
         </is>
       </c>
     </row>
@@ -18437,7 +18437,7 @@
       </c>
       <c r="C1008" t="inlineStr">
         <is>
-          <t>Forest</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -18488,7 +18488,7 @@
       </c>
       <c r="C1011" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -18505,7 +18505,7 @@
       </c>
       <c r="C1012" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -18522,7 +18522,7 @@
       </c>
       <c r="C1013" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Street</t>
         </is>
       </c>
     </row>
@@ -18573,7 +18573,7 @@
       </c>
       <c r="C1016" t="inlineStr">
         <is>
-          <t>Mountain</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -18590,7 +18590,7 @@
       </c>
       <c r="C1017" t="inlineStr">
         <is>
-          <t>Forest</t>
+          <t>Mountain</t>
         </is>
       </c>
     </row>
@@ -18624,7 +18624,7 @@
       </c>
       <c r="C1019" t="inlineStr">
         <is>
-          <t>Mountain</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -18641,7 +18641,7 @@
       </c>
       <c r="C1020" t="inlineStr">
         <is>
-          <t>Open country</t>
+          <t>Mountain</t>
         </is>
       </c>
     </row>
@@ -18692,7 +18692,7 @@
       </c>
       <c r="C1023" t="inlineStr">
         <is>
-          <t>Forest</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -18811,7 +18811,7 @@
       </c>
       <c r="C1030" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -18879,7 +18879,7 @@
       </c>
       <c r="C1034" t="inlineStr">
         <is>
-          <t>Mountain</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -18930,7 +18930,7 @@
       </c>
       <c r="C1037" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -18964,7 +18964,7 @@
       </c>
       <c r="C1039" t="inlineStr">
         <is>
-          <t>Forest</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -18998,7 +18998,7 @@
       </c>
       <c r="C1041" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -19015,7 +19015,7 @@
       </c>
       <c r="C1042" t="inlineStr">
         <is>
-          <t>Street</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -19032,7 +19032,7 @@
       </c>
       <c r="C1043" t="inlineStr">
         <is>
-          <t>Forest</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -19066,7 +19066,7 @@
       </c>
       <c r="C1045" t="inlineStr">
         <is>
-          <t>Mountain</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -19083,7 +19083,7 @@
       </c>
       <c r="C1046" t="inlineStr">
         <is>
-          <t>Mountain</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -19100,7 +19100,7 @@
       </c>
       <c r="C1047" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -19117,7 +19117,7 @@
       </c>
       <c r="C1048" t="inlineStr">
         <is>
-          <t>Forest</t>
+          <t>Mountain</t>
         </is>
       </c>
     </row>
@@ -19185,7 +19185,7 @@
       </c>
       <c r="C1052" t="inlineStr">
         <is>
-          <t>Forest</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -19202,7 +19202,7 @@
       </c>
       <c r="C1053" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -19236,7 +19236,7 @@
       </c>
       <c r="C1055" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -19253,7 +19253,7 @@
       </c>
       <c r="C1056" t="inlineStr">
         <is>
-          <t>Forest</t>
+          <t>Mountain</t>
         </is>
       </c>
     </row>
@@ -19270,7 +19270,7 @@
       </c>
       <c r="C1057" t="inlineStr">
         <is>
-          <t>Mountain</t>
+          <t>Street</t>
         </is>
       </c>
     </row>
@@ -19304,7 +19304,7 @@
       </c>
       <c r="C1059" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -19321,7 +19321,7 @@
       </c>
       <c r="C1060" t="inlineStr">
         <is>
-          <t>Forest</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -19338,7 +19338,7 @@
       </c>
       <c r="C1061" t="inlineStr">
         <is>
-          <t>Forest</t>
+          <t>Mountain</t>
         </is>
       </c>
     </row>
@@ -19406,7 +19406,7 @@
       </c>
       <c r="C1065" t="inlineStr">
         <is>
-          <t>Mountain</t>
+          <t>Coast</t>
         </is>
       </c>
     </row>
@@ -19423,7 +19423,7 @@
       </c>
       <c r="C1066" t="inlineStr">
         <is>
-          <t>Forest</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -19440,7 +19440,7 @@
       </c>
       <c r="C1067" t="inlineStr">
         <is>
-          <t>Forest</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -19457,7 +19457,7 @@
       </c>
       <c r="C1068" t="inlineStr">
         <is>
-          <t>Forest</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -19491,7 +19491,7 @@
       </c>
       <c r="C1070" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -19508,7 +19508,7 @@
       </c>
       <c r="C1071" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -19542,7 +19542,7 @@
       </c>
       <c r="C1073" t="inlineStr">
         <is>
-          <t>Street</t>
+          <t>Mountain</t>
         </is>
       </c>
     </row>
@@ -19559,7 +19559,7 @@
       </c>
       <c r="C1074" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -19593,7 +19593,7 @@
       </c>
       <c r="C1076" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -19610,7 +19610,7 @@
       </c>
       <c r="C1077" t="inlineStr">
         <is>
-          <t>Forest</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -19627,7 +19627,7 @@
       </c>
       <c r="C1078" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -19644,7 +19644,7 @@
       </c>
       <c r="C1079" t="inlineStr">
         <is>
-          <t>Forest</t>
+          <t>Mountain</t>
         </is>
       </c>
     </row>
@@ -19661,7 +19661,7 @@
       </c>
       <c r="C1080" t="inlineStr">
         <is>
-          <t>Forest</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -19678,7 +19678,7 @@
       </c>
       <c r="C1081" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Mountain</t>
         </is>
       </c>
     </row>
@@ -19695,7 +19695,7 @@
       </c>
       <c r="C1082" t="inlineStr">
         <is>
-          <t>Forest</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -19712,7 +19712,7 @@
       </c>
       <c r="C1083" t="inlineStr">
         <is>
-          <t>Open country</t>
+          <t>Mountain</t>
         </is>
       </c>
     </row>
@@ -19831,7 +19831,7 @@
       </c>
       <c r="C1090" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Mountain</t>
         </is>
       </c>
     </row>
@@ -19848,7 +19848,7 @@
       </c>
       <c r="C1091" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -19865,7 +19865,7 @@
       </c>
       <c r="C1092" t="inlineStr">
         <is>
-          <t>Forest</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -19882,7 +19882,7 @@
       </c>
       <c r="C1093" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -19933,7 +19933,7 @@
       </c>
       <c r="C1096" t="inlineStr">
         <is>
-          <t>Forest</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -19984,7 +19984,7 @@
       </c>
       <c r="C1099" t="inlineStr">
         <is>
-          <t>Mountain</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -20001,7 +20001,7 @@
       </c>
       <c r="C1100" t="inlineStr">
         <is>
-          <t>Mountain</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -20018,7 +20018,7 @@
       </c>
       <c r="C1101" t="inlineStr">
         <is>
-          <t>Forest</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -20086,7 +20086,7 @@
       </c>
       <c r="C1105" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Bedroom</t>
         </is>
       </c>
     </row>
@@ -20154,7 +20154,7 @@
       </c>
       <c r="C1109" t="inlineStr">
         <is>
-          <t>Street</t>
+          <t>Mountain</t>
         </is>
       </c>
     </row>
@@ -20273,7 +20273,7 @@
       </c>
       <c r="C1116" t="inlineStr">
         <is>
-          <t>Street</t>
+          <t>Inside city</t>
         </is>
       </c>
     </row>
@@ -20290,7 +20290,7 @@
       </c>
       <c r="C1117" t="inlineStr">
         <is>
-          <t>Bedroom</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -20477,7 +20477,7 @@
       </c>
       <c r="C1128" t="inlineStr">
         <is>
-          <t>Inside city</t>
+          <t>Store</t>
         </is>
       </c>
     </row>
@@ -20511,7 +20511,7 @@
       </c>
       <c r="C1130" t="inlineStr">
         <is>
-          <t>Office</t>
+          <t>Inside city</t>
         </is>
       </c>
     </row>
@@ -20528,7 +20528,7 @@
       </c>
       <c r="C1131" t="inlineStr">
         <is>
-          <t>Bedroom</t>
+          <t>Store</t>
         </is>
       </c>
     </row>
@@ -20630,7 +20630,7 @@
       </c>
       <c r="C1137" t="inlineStr">
         <is>
-          <t>Kitchen</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -20681,7 +20681,7 @@
       </c>
       <c r="C1140" t="inlineStr">
         <is>
-          <t>Mountain</t>
+          <t>Store</t>
         </is>
       </c>
     </row>
@@ -20698,7 +20698,7 @@
       </c>
       <c r="C1141" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Inside city</t>
         </is>
       </c>
     </row>
@@ -20834,7 +20834,7 @@
       </c>
       <c r="C1149" t="inlineStr">
         <is>
-          <t>Kitchen</t>
+          <t>Bedroom</t>
         </is>
       </c>
     </row>
@@ -20868,7 +20868,7 @@
       </c>
       <c r="C1151" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Street</t>
         </is>
       </c>
     </row>
@@ -20953,7 +20953,7 @@
       </c>
       <c r="C1156" t="inlineStr">
         <is>
-          <t>Store</t>
+          <t>Suburb</t>
         </is>
       </c>
     </row>
@@ -20987,7 +20987,7 @@
       </c>
       <c r="C1158" t="inlineStr">
         <is>
-          <t>Inside city</t>
+          <t>Store</t>
         </is>
       </c>
     </row>
@@ -21055,7 +21055,7 @@
       </c>
       <c r="C1162" t="inlineStr">
         <is>
-          <t>Suburb</t>
+          <t>Store</t>
         </is>
       </c>
     </row>
@@ -21072,7 +21072,7 @@
       </c>
       <c r="C1163" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Store</t>
         </is>
       </c>
     </row>
@@ -21157,7 +21157,7 @@
       </c>
       <c r="C1168" t="inlineStr">
         <is>
-          <t>Store</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -21310,7 +21310,7 @@
       </c>
       <c r="C1177" t="inlineStr">
         <is>
-          <t>Office</t>
+          <t>Kitchen</t>
         </is>
       </c>
     </row>
@@ -21378,7 +21378,7 @@
       </c>
       <c r="C1181" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Store</t>
         </is>
       </c>
     </row>
@@ -21446,7 +21446,7 @@
       </c>
       <c r="C1185" t="inlineStr">
         <is>
-          <t>Street</t>
+          <t>Suburb</t>
         </is>
       </c>
     </row>
@@ -21565,7 +21565,7 @@
       </c>
       <c r="C1192" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Street</t>
         </is>
       </c>
     </row>
@@ -21582,7 +21582,7 @@
       </c>
       <c r="C1193" t="inlineStr">
         <is>
-          <t>Inside city</t>
+          <t>Store</t>
         </is>
       </c>
     </row>
@@ -21650,7 +21650,7 @@
       </c>
       <c r="C1197" t="inlineStr">
         <is>
-          <t>Suburb</t>
+          <t>Store</t>
         </is>
       </c>
     </row>
@@ -21684,7 +21684,7 @@
       </c>
       <c r="C1199" t="inlineStr">
         <is>
-          <t>Street</t>
+          <t>Store</t>
         </is>
       </c>
     </row>
@@ -21701,7 +21701,7 @@
       </c>
       <c r="C1200" t="inlineStr">
         <is>
-          <t>Street</t>
+          <t>Store</t>
         </is>
       </c>
     </row>
@@ -21718,7 +21718,7 @@
       </c>
       <c r="C1201" t="inlineStr">
         <is>
-          <t>Store</t>
+          <t>Forest</t>
         </is>
       </c>
     </row>
@@ -21735,7 +21735,7 @@
       </c>
       <c r="C1202" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Street</t>
         </is>
       </c>
     </row>
@@ -21786,7 +21786,7 @@
       </c>
       <c r="C1205" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Tall building</t>
         </is>
       </c>
     </row>
@@ -21803,7 +21803,7 @@
       </c>
       <c r="C1206" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Inside city</t>
         </is>
       </c>
     </row>
@@ -21837,7 +21837,7 @@
       </c>
       <c r="C1208" t="inlineStr">
         <is>
-          <t>Street</t>
+          <t>Bedroom</t>
         </is>
       </c>
     </row>
@@ -21871,7 +21871,7 @@
       </c>
       <c r="C1210" t="inlineStr">
         <is>
-          <t>Street</t>
+          <t>Store</t>
         </is>
       </c>
     </row>
@@ -21973,7 +21973,7 @@
       </c>
       <c r="C1216" t="inlineStr">
         <is>
-          <t>Open country</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -21990,7 +21990,7 @@
       </c>
       <c r="C1217" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Inside city</t>
         </is>
       </c>
     </row>
@@ -22007,7 +22007,7 @@
       </c>
       <c r="C1218" t="inlineStr">
         <is>
-          <t>Street</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -22058,7 +22058,7 @@
       </c>
       <c r="C1221" t="inlineStr">
         <is>
-          <t>Inside city</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -22075,7 +22075,7 @@
       </c>
       <c r="C1222" t="inlineStr">
         <is>
-          <t>Street</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -22092,7 +22092,7 @@
       </c>
       <c r="C1223" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Inside city</t>
         </is>
       </c>
     </row>
@@ -22109,7 +22109,7 @@
       </c>
       <c r="C1224" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Street</t>
         </is>
       </c>
     </row>
@@ -22126,7 +22126,7 @@
       </c>
       <c r="C1225" t="inlineStr">
         <is>
-          <t>Street</t>
+          <t>Tall building</t>
         </is>
       </c>
     </row>
@@ -22160,7 +22160,7 @@
       </c>
       <c r="C1227" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Mountain</t>
         </is>
       </c>
     </row>
@@ -22194,7 +22194,7 @@
       </c>
       <c r="C1229" t="inlineStr">
         <is>
-          <t>Street</t>
+          <t>Suburb</t>
         </is>
       </c>
     </row>
@@ -22245,7 +22245,7 @@
       </c>
       <c r="C1232" t="inlineStr">
         <is>
-          <t>Street</t>
+          <t>Tall building</t>
         </is>
       </c>
     </row>
@@ -22279,7 +22279,7 @@
       </c>
       <c r="C1234" t="inlineStr">
         <is>
-          <t>Street</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -22296,7 +22296,7 @@
       </c>
       <c r="C1235" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Street</t>
         </is>
       </c>
     </row>
@@ -22415,7 +22415,7 @@
       </c>
       <c r="C1242" t="inlineStr">
         <is>
-          <t>Street</t>
+          <t>Mountain</t>
         </is>
       </c>
     </row>
@@ -22432,7 +22432,7 @@
       </c>
       <c r="C1243" t="inlineStr">
         <is>
-          <t>Inside city</t>
+          <t>Street</t>
         </is>
       </c>
     </row>
@@ -22449,7 +22449,7 @@
       </c>
       <c r="C1244" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Tall building</t>
         </is>
       </c>
     </row>
@@ -22483,7 +22483,7 @@
       </c>
       <c r="C1246" t="inlineStr">
         <is>
-          <t>Street</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -22517,7 +22517,7 @@
       </c>
       <c r="C1248" t="inlineStr">
         <is>
-          <t>Street</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -22534,7 +22534,7 @@
       </c>
       <c r="C1249" t="inlineStr">
         <is>
-          <t>Street</t>
+          <t>Tall building</t>
         </is>
       </c>
     </row>
@@ -22568,7 +22568,7 @@
       </c>
       <c r="C1251" t="inlineStr">
         <is>
-          <t>Street</t>
+          <t>Store</t>
         </is>
       </c>
     </row>
@@ -22704,7 +22704,7 @@
       </c>
       <c r="C1259" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -22721,7 +22721,7 @@
       </c>
       <c r="C1260" t="inlineStr">
         <is>
-          <t>Street</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -22738,7 +22738,7 @@
       </c>
       <c r="C1261" t="inlineStr">
         <is>
-          <t>Street</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -22772,7 +22772,7 @@
       </c>
       <c r="C1263" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Mountain</t>
         </is>
       </c>
     </row>
@@ -22789,7 +22789,7 @@
       </c>
       <c r="C1264" t="inlineStr">
         <is>
-          <t>Street</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -22823,7 +22823,7 @@
       </c>
       <c r="C1266" t="inlineStr">
         <is>
-          <t>Forest</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -22857,7 +22857,7 @@
       </c>
       <c r="C1268" t="inlineStr">
         <is>
-          <t>Street</t>
+          <t>Mountain</t>
         </is>
       </c>
     </row>
@@ -22891,7 +22891,7 @@
       </c>
       <c r="C1270" t="inlineStr">
         <is>
-          <t>Street</t>
+          <t>Coast</t>
         </is>
       </c>
     </row>
@@ -22908,7 +22908,7 @@
       </c>
       <c r="C1271" t="inlineStr">
         <is>
-          <t>Store</t>
+          <t>Street</t>
         </is>
       </c>
     </row>
@@ -22959,7 +22959,7 @@
       </c>
       <c r="C1274" t="inlineStr">
         <is>
-          <t>Street</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -23027,7 +23027,7 @@
       </c>
       <c r="C1278" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Street</t>
         </is>
       </c>
     </row>
@@ -23078,7 +23078,7 @@
       </c>
       <c r="C1281" t="inlineStr">
         <is>
-          <t>Street</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -23197,7 +23197,7 @@
       </c>
       <c r="C1288" t="inlineStr">
         <is>
-          <t>Store</t>
+          <t>Forest</t>
         </is>
       </c>
     </row>
@@ -23214,7 +23214,7 @@
       </c>
       <c r="C1289" t="inlineStr">
         <is>
-          <t>Inside city</t>
+          <t>Tall building</t>
         </is>
       </c>
     </row>
@@ -23282,7 +23282,7 @@
       </c>
       <c r="C1293" t="inlineStr">
         <is>
-          <t>Store</t>
+          <t>Street</t>
         </is>
       </c>
     </row>
@@ -23316,7 +23316,7 @@
       </c>
       <c r="C1295" t="inlineStr">
         <is>
-          <t>Suburb</t>
+          <t>Store</t>
         </is>
       </c>
     </row>
@@ -23367,7 +23367,7 @@
       </c>
       <c r="C1298" t="inlineStr">
         <is>
-          <t>Store</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -23639,7 +23639,7 @@
       </c>
       <c r="C1314" t="inlineStr">
         <is>
-          <t>Suburb</t>
+          <t>Forest</t>
         </is>
       </c>
     </row>
@@ -23758,7 +23758,7 @@
       </c>
       <c r="C1321" t="inlineStr">
         <is>
-          <t>Suburb</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -23775,7 +23775,7 @@
       </c>
       <c r="C1322" t="inlineStr">
         <is>
-          <t>Suburb</t>
+          <t>Forest</t>
         </is>
       </c>
     </row>
@@ -23792,7 +23792,7 @@
       </c>
       <c r="C1323" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -23843,7 +23843,7 @@
       </c>
       <c r="C1326" t="inlineStr">
         <is>
-          <t>Forest</t>
+          <t>Store</t>
         </is>
       </c>
     </row>
@@ -23894,7 +23894,7 @@
       </c>
       <c r="C1329" t="inlineStr">
         <is>
-          <t>Living room</t>
+          <t>Suburb</t>
         </is>
       </c>
     </row>
@@ -23928,7 +23928,7 @@
       </c>
       <c r="C1331" t="inlineStr">
         <is>
-          <t>Store</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -24013,7 +24013,7 @@
       </c>
       <c r="C1336" t="inlineStr">
         <is>
-          <t>Suburb</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -24064,7 +24064,7 @@
       </c>
       <c r="C1339" t="inlineStr">
         <is>
-          <t>Suburb</t>
+          <t>Store</t>
         </is>
       </c>
     </row>
@@ -24098,7 +24098,7 @@
       </c>
       <c r="C1341" t="inlineStr">
         <is>
-          <t>Suburb</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -24353,7 +24353,7 @@
       </c>
       <c r="C1356" t="inlineStr">
         <is>
-          <t>Suburb</t>
+          <t>Store</t>
         </is>
       </c>
     </row>
@@ -24370,7 +24370,7 @@
       </c>
       <c r="C1357" t="inlineStr">
         <is>
-          <t>Suburb</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -24523,7 +24523,7 @@
       </c>
       <c r="C1366" t="inlineStr">
         <is>
-          <t>Suburb</t>
+          <t>Forest</t>
         </is>
       </c>
     </row>
@@ -24557,7 +24557,7 @@
       </c>
       <c r="C1368" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Highway</t>
         </is>
       </c>
     </row>
@@ -24676,7 +24676,7 @@
       </c>
       <c r="C1375" t="inlineStr">
         <is>
-          <t>Suburb</t>
+          <t>Store</t>
         </is>
       </c>
     </row>
@@ -24761,7 +24761,7 @@
       </c>
       <c r="C1380" t="inlineStr">
         <is>
-          <t>Store</t>
+          <t>Suburb</t>
         </is>
       </c>
     </row>
@@ -24982,7 +24982,7 @@
       </c>
       <c r="C1393" t="inlineStr">
         <is>
-          <t>Suburb</t>
+          <t>Living room</t>
         </is>
       </c>
     </row>
@@ -25016,7 +25016,7 @@
       </c>
       <c r="C1395" t="inlineStr">
         <is>
-          <t>Suburb</t>
+          <t>Mountain</t>
         </is>
       </c>
     </row>
@@ -25050,7 +25050,7 @@
       </c>
       <c r="C1397" t="inlineStr">
         <is>
-          <t>Forest</t>
+          <t>Mountain</t>
         </is>
       </c>
     </row>
@@ -25118,7 +25118,7 @@
       </c>
       <c r="C1401" t="inlineStr">
         <is>
-          <t>Suburb</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -25135,7 +25135,7 @@
       </c>
       <c r="C1402" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Tall building</t>
         </is>
       </c>
     </row>
@@ -25152,7 +25152,7 @@
       </c>
       <c r="C1403" t="inlineStr">
         <is>
-          <t>Store</t>
+          <t>Tall building</t>
         </is>
       </c>
     </row>
@@ -25186,7 +25186,7 @@
       </c>
       <c r="C1405" t="inlineStr">
         <is>
-          <t>Bedroom</t>
+          <t>Tall building</t>
         </is>
       </c>
     </row>
@@ -25237,7 +25237,7 @@
       </c>
       <c r="C1408" t="inlineStr">
         <is>
-          <t>Tall building</t>
+          <t>Forest</t>
         </is>
       </c>
     </row>
@@ -25305,7 +25305,7 @@
       </c>
       <c r="C1412" t="inlineStr">
         <is>
-          <t>Street</t>
+          <t>Tall building</t>
         </is>
       </c>
     </row>
@@ -25441,7 +25441,7 @@
       </c>
       <c r="C1420" t="inlineStr">
         <is>
-          <t>Street</t>
+          <t>Tall building</t>
         </is>
       </c>
     </row>
@@ -25509,7 +25509,7 @@
       </c>
       <c r="C1424" t="inlineStr">
         <is>
-          <t>Tall building</t>
+          <t>Coast</t>
         </is>
       </c>
     </row>
@@ -25543,7 +25543,7 @@
       </c>
       <c r="C1426" t="inlineStr">
         <is>
-          <t>Inside city</t>
+          <t>Tall building</t>
         </is>
       </c>
     </row>
@@ -25594,7 +25594,7 @@
       </c>
       <c r="C1429" t="inlineStr">
         <is>
-          <t>Tall building</t>
+          <t>Coast</t>
         </is>
       </c>
     </row>
@@ -25628,7 +25628,7 @@
       </c>
       <c r="C1431" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Tall building</t>
         </is>
       </c>
     </row>
@@ -25645,7 +25645,7 @@
       </c>
       <c r="C1432" t="inlineStr">
         <is>
-          <t>Inside city</t>
+          <t>Tall building</t>
         </is>
       </c>
     </row>
@@ -25662,7 +25662,7 @@
       </c>
       <c r="C1433" t="inlineStr">
         <is>
-          <t>Store</t>
+          <t>Tall building</t>
         </is>
       </c>
     </row>
@@ -25730,7 +25730,7 @@
       </c>
       <c r="C1437" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Tall building</t>
         </is>
       </c>
     </row>
@@ -25747,7 +25747,7 @@
       </c>
       <c r="C1438" t="inlineStr">
         <is>
-          <t>Tall building</t>
+          <t>Forest</t>
         </is>
       </c>
     </row>
@@ -25764,7 +25764,7 @@
       </c>
       <c r="C1439" t="inlineStr">
         <is>
-          <t>Inside city</t>
+          <t>Tall building</t>
         </is>
       </c>
     </row>
@@ -25781,7 +25781,7 @@
       </c>
       <c r="C1440" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Inside city</t>
         </is>
       </c>
     </row>
@@ -25798,7 +25798,7 @@
       </c>
       <c r="C1441" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Tall building</t>
         </is>
       </c>
     </row>
@@ -25832,7 +25832,7 @@
       </c>
       <c r="C1443" t="inlineStr">
         <is>
-          <t>Inside city</t>
+          <t>Tall building</t>
         </is>
       </c>
     </row>
@@ -25849,7 +25849,7 @@
       </c>
       <c r="C1444" t="inlineStr">
         <is>
-          <t>Inside city</t>
+          <t>Tall building</t>
         </is>
       </c>
     </row>
@@ -25866,7 +25866,7 @@
       </c>
       <c r="C1445" t="inlineStr">
         <is>
-          <t>Store</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -25951,7 +25951,7 @@
       </c>
       <c r="C1450" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Street</t>
         </is>
       </c>
     </row>
@@ -25985,7 +25985,7 @@
       </c>
       <c r="C1452" t="inlineStr">
         <is>
-          <t>Inside city</t>
+          <t>Tall building</t>
         </is>
       </c>
     </row>
@@ -26019,7 +26019,7 @@
       </c>
       <c r="C1454" t="inlineStr">
         <is>
-          <t>Forest</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -26087,7 +26087,7 @@
       </c>
       <c r="C1458" t="inlineStr">
         <is>
-          <t>Open country</t>
+          <t>Coast</t>
         </is>
       </c>
     </row>
@@ -26138,7 +26138,7 @@
       </c>
       <c r="C1461" t="inlineStr">
         <is>
-          <t>Inside city</t>
+          <t>Tall building</t>
         </is>
       </c>
     </row>
@@ -26155,7 +26155,7 @@
       </c>
       <c r="C1462" t="inlineStr">
         <is>
-          <t>Street</t>
+          <t>Tall building</t>
         </is>
       </c>
     </row>
@@ -26172,7 +26172,7 @@
       </c>
       <c r="C1463" t="inlineStr">
         <is>
-          <t>Street</t>
+          <t>Mountain</t>
         </is>
       </c>
     </row>
@@ -26206,7 +26206,7 @@
       </c>
       <c r="C1465" t="inlineStr">
         <is>
-          <t>Street</t>
+          <t>Tall building</t>
         </is>
       </c>
     </row>
@@ -26223,7 +26223,7 @@
       </c>
       <c r="C1466" t="inlineStr">
         <is>
-          <t>Inside city</t>
+          <t>Tall building</t>
         </is>
       </c>
     </row>
@@ -26257,7 +26257,7 @@
       </c>
       <c r="C1468" t="inlineStr">
         <is>
-          <t>Street</t>
+          <t>Tall building</t>
         </is>
       </c>
     </row>
@@ -26291,7 +26291,7 @@
       </c>
       <c r="C1470" t="inlineStr">
         <is>
-          <t>Tall building</t>
+          <t>Coast</t>
         </is>
       </c>
     </row>
@@ -26325,7 +26325,7 @@
       </c>
       <c r="C1472" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Tall building</t>
         </is>
       </c>
     </row>
@@ -26342,7 +26342,7 @@
       </c>
       <c r="C1473" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Tall building</t>
         </is>
       </c>
     </row>
@@ -26376,7 +26376,7 @@
       </c>
       <c r="C1475" t="inlineStr">
         <is>
-          <t>Inside city</t>
+          <t>Tall building</t>
         </is>
       </c>
     </row>
@@ -26393,7 +26393,7 @@
       </c>
       <c r="C1476" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Tall building</t>
         </is>
       </c>
     </row>
@@ -26410,7 +26410,7 @@
       </c>
       <c r="C1477" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -26444,7 +26444,7 @@
       </c>
       <c r="C1479" t="inlineStr">
         <is>
-          <t>Open country</t>
+          <t>Coast</t>
         </is>
       </c>
     </row>
@@ -26478,7 +26478,7 @@
       </c>
       <c r="C1481" t="inlineStr">
         <is>
-          <t>Bedroom</t>
+          <t>Suburb</t>
         </is>
       </c>
     </row>
@@ -26512,7 +26512,7 @@
       </c>
       <c r="C1483" t="inlineStr">
         <is>
-          <t>Bedroom</t>
+          <t>Office</t>
         </is>
       </c>
     </row>
@@ -26580,7 +26580,7 @@
       </c>
       <c r="C1487" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Tall building</t>
         </is>
       </c>
     </row>
@@ -26614,7 +26614,7 @@
       </c>
       <c r="C1489" t="inlineStr">
         <is>
-          <t>Mountain</t>
+          <t>Open country</t>
         </is>
       </c>
     </row>
@@ -26631,7 +26631,7 @@
       </c>
       <c r="C1490" t="inlineStr">
         <is>
-          <t>Highway</t>
+          <t>Tall building</t>
         </is>
       </c>
     </row>
@@ -26733,7 +26733,7 @@
       </c>
       <c r="C1496" t="inlineStr">
         <is>
-          <t>Store</t>
+          <t>Tall building</t>
         </is>
       </c>
     </row>
@@ -26767,7 +26767,7 @@
       </c>
       <c r="C1498" t="inlineStr">
         <is>
-          <t>Coast</t>
+          <t>Tall building</t>
         </is>
       </c>
     </row>
